--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -450,22 +450,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.70781</v>
+        <v>17.352</v>
       </c>
       <c r="D2" t="n">
-        <v>16.61096</v>
+        <v>16.81974</v>
       </c>
       <c r="E2" t="n">
-        <v>16.93842</v>
+        <v>16.93597</v>
       </c>
       <c r="F2" t="n">
-        <v>43.26922</v>
+        <v>43.06717</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05104</v>
+        <v>0.05103</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85944</v>
+        <v>1.84328</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +475,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.00969</v>
+        <v>17.06816</v>
       </c>
       <c r="D3" t="n">
-        <v>16.80518</v>
+        <v>16.66827</v>
       </c>
       <c r="E3" t="n">
-        <v>17.37209</v>
+        <v>16.85537</v>
       </c>
       <c r="F3" t="n">
-        <v>42.77843</v>
+        <v>42.97436</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05163</v>
+        <v>0.05227</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83076</v>
+        <v>1.82448</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +500,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.01881</v>
+        <v>17.16235</v>
       </c>
       <c r="D4" t="n">
-        <v>16.67899</v>
+        <v>16.71294</v>
       </c>
       <c r="E4" t="n">
-        <v>16.82923</v>
+        <v>17.0009</v>
       </c>
       <c r="F4" t="n">
-        <v>42.46539</v>
+        <v>42.74485</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05158</v>
+        <v>0.05039</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89442</v>
+        <v>1.87244</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +525,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.70651</v>
+        <v>16.90414</v>
       </c>
       <c r="D5" t="n">
-        <v>17.07727</v>
+        <v>16.68903</v>
       </c>
       <c r="E5" t="n">
-        <v>17.20439</v>
+        <v>16.89569</v>
       </c>
       <c r="F5" t="n">
-        <v>42.22679</v>
+        <v>43.31141</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05064</v>
+        <v>0.05233</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8355</v>
+        <v>1.82793</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +550,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.01744</v>
+        <v>17.31748</v>
       </c>
       <c r="D6" t="n">
-        <v>16.48763</v>
+        <v>16.63691</v>
       </c>
       <c r="E6" t="n">
-        <v>16.71922</v>
+        <v>17.06685</v>
       </c>
       <c r="F6" t="n">
-        <v>41.96217</v>
+        <v>43.55072</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0516</v>
+        <v>0.05186</v>
       </c>
       <c r="H6" t="n">
-        <v>1.86244</v>
+        <v>1.87106</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +575,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.94333</v>
+        <v>17.03473</v>
       </c>
       <c r="D7" t="n">
-        <v>17.09965</v>
+        <v>16.76216</v>
       </c>
       <c r="E7" t="n">
-        <v>16.46131</v>
+        <v>16.90555</v>
       </c>
       <c r="F7" t="n">
-        <v>43.60466</v>
+        <v>43.49022</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05029</v>
+        <v>0.05147</v>
       </c>
       <c r="H7" t="n">
-        <v>1.87329</v>
+        <v>1.82036</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.81509</v>
+        <v>17.29781</v>
       </c>
       <c r="D8" t="n">
-        <v>17.00057</v>
+        <v>16.41605</v>
       </c>
       <c r="E8" t="n">
-        <v>16.59989</v>
+        <v>16.78462</v>
       </c>
       <c r="F8" t="n">
-        <v>43.64564</v>
+        <v>42.32188</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05147</v>
+        <v>0.05092</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85783</v>
+        <v>1.81696</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +625,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.97849</v>
+        <v>17.08887</v>
       </c>
       <c r="D9" t="n">
-        <v>16.70495</v>
+        <v>16.614</v>
       </c>
       <c r="E9" t="n">
-        <v>16.92177</v>
+        <v>16.79079</v>
       </c>
       <c r="F9" t="n">
-        <v>43.29217</v>
+        <v>43.16107</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05082</v>
+        <v>0.05192</v>
       </c>
       <c r="H9" t="n">
-        <v>1.85015</v>
+        <v>1.83168</v>
       </c>
     </row>
     <row r="10">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.06679</v>
+        <v>16.81528</v>
       </c>
       <c r="D10" t="n">
-        <v>16.45813</v>
+        <v>16.67473</v>
       </c>
       <c r="E10" t="n">
-        <v>17.26044</v>
+        <v>16.73353</v>
       </c>
       <c r="F10" t="n">
-        <v>44.53417</v>
+        <v>43.76075</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05263</v>
+        <v>0.05025</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85196</v>
+        <v>1.88086</v>
       </c>
     </row>
     <row r="11">
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60978</v>
+        <v>0.62168</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10528</v>
+        <v>1.09321</v>
       </c>
     </row>
     <row r="13">
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.61477</v>
+        <v>0.60943</v>
       </c>
       <c r="D13" t="n">
-        <v>1.13582</v>
+        <v>1.13541</v>
       </c>
     </row>
     <row r="14">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6176700000000001</v>
+        <v>0.62574</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11416</v>
+        <v>1.112</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.61193</v>
+        <v>0.61666</v>
       </c>
       <c r="D15" t="n">
-        <v>1.14061</v>
+        <v>1.11075</v>
       </c>
     </row>
     <row r="16">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.61546</v>
+        <v>0.61449</v>
       </c>
       <c r="D16" t="n">
-        <v>1.14504</v>
+        <v>1.14071</v>
       </c>
     </row>
     <row r="17">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.60959</v>
+        <v>0.61615</v>
       </c>
       <c r="D17" t="n">
-        <v>1.12884</v>
+        <v>1.14045</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.62098</v>
+        <v>0.62562</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13505</v>
+        <v>1.12789</v>
       </c>
     </row>
     <row r="19">
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.63253</v>
+        <v>0.6199</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12402</v>
+        <v>1.11654</v>
       </c>
     </row>
     <row r="20">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60358</v>
+        <v>0.61629</v>
       </c>
       <c r="D20" t="n">
-        <v>1.14669</v>
+        <v>1.14522</v>
       </c>
     </row>
   </sheetData>
